--- a/vse-loti/341306984/spec-341306984.xlsx
+++ b/vse-loti/341306984/spec-341306984.xlsx
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +96,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -464,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1146,26 +1149,33 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>НМЦК с НДС 22%:</t>
+          <t>НМЦК с НДС 22% (справочно):</t>
         </is>
       </c>
       <c r="F21" s="8" t="n">
         <v>5026523.74</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Ставка НДС в документах не указана, расчёт справочный по 22 %; суммы источника указаны с НДС: "с учетом всех налогов и сборов" — Документация изм.rar → Приложение №3 - Обоснование НМЦ.xls. «с НДС» — сумма из документа, «без НДС» = сумма ÷ 1,22.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>Источник: Документация изм.rar → Приложение №3 - Обоснование НМЦ.xls
 Документация изм.rar → Извещение запрос цен свыше 500 с НДС.docx</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25"/>
+    <row r="26"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A23:B25"/>
+    <mergeCell ref="A24:B26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vse-loti/341306984/spec-341306984.xlsx
+++ b/vse-loti/341306984/spec-341306984.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -479,6 +479,7 @@
     <col width="20.28515625" customWidth="1" min="7" max="7"/>
     <col width="18.85546875" customWidth="1" min="8" max="8"/>
     <col width="16.42578125" customWidth="1" min="9" max="9"/>
+    <col width="18.85546875" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -514,17 +515,22 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Цена за т (без НДС)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Стоимость (с НДС)</t>
         </is>
       </c>
     </row>
@@ -554,13 +560,16 @@
         <v>0.364</v>
       </c>
       <c r="G2" s="5" t="n">
+        <v>266598.36</v>
+      </c>
+      <c r="H2" s="5" t="n">
         <v>97041.8</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>266598.36</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>325250</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>118391</v>
       </c>
     </row>
     <row r="3">
@@ -589,13 +598,16 @@
         <v>0.364</v>
       </c>
       <c r="G3" s="5" t="n">
+        <v>395013.66</v>
+      </c>
+      <c r="H3" s="5" t="n">
         <v>143784.97</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>395013.66</v>
       </c>
       <c r="I3" s="5" t="n">
         <v>481916.67</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>175417.66</v>
       </c>
     </row>
     <row r="4">
@@ -624,13 +636,16 @@
         <v>0.441</v>
       </c>
       <c r="G4" s="5" t="n">
+        <v>211407.1</v>
+      </c>
+      <c r="H4" s="5" t="n">
         <v>93230.53</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>211407.1</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>257916.66</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>113741.25</v>
       </c>
     </row>
     <row r="5">
@@ -659,13 +674,16 @@
         <v>0.708</v>
       </c>
       <c r="G5" s="5" t="n">
+        <v>211407.1</v>
+      </c>
+      <c r="H5" s="5" t="n">
         <v>149676.23</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>211407.1</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>257916.66</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>182605</v>
       </c>
     </row>
     <row r="6">
@@ -694,13 +712,16 @@
         <v>0.481</v>
       </c>
       <c r="G6" s="5" t="n">
+        <v>211407.1</v>
+      </c>
+      <c r="H6" s="5" t="n">
         <v>101686.82</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>211407.1</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>257916.66</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>124057.92</v>
       </c>
     </row>
     <row r="7">
@@ -729,13 +750,16 @@
         <v>0.749</v>
       </c>
       <c r="G7" s="5" t="n">
+        <v>218237.7</v>
+      </c>
+      <c r="H7" s="5" t="n">
         <v>163460.04</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>218237.7</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>266249.99</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>199421.25</v>
       </c>
     </row>
     <row r="8">
@@ -764,13 +788,16 @@
         <v>0.8169999999999999</v>
       </c>
       <c r="G8" s="5" t="n">
+        <v>403210.38</v>
+      </c>
+      <c r="H8" s="5" t="n">
         <v>329422.88</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>403210.38</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>491916.66</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>401895.91</v>
       </c>
     </row>
     <row r="9">
@@ -799,13 +826,16 @@
         <v>0.9320000000000001</v>
       </c>
       <c r="G9" s="5" t="n">
+        <v>219603.83</v>
+      </c>
+      <c r="H9" s="5" t="n">
         <v>204670.77</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>219603.83</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>267916.67</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>249698.34</v>
       </c>
     </row>
     <row r="10">
@@ -834,13 +864,16 @@
         <v>1.219</v>
       </c>
       <c r="G10" s="5" t="n">
+        <v>219603.83</v>
+      </c>
+      <c r="H10" s="5" t="n">
         <v>267697.07</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>219603.83</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>267916.67</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>326590.43</v>
       </c>
     </row>
     <row r="11">
@@ -869,13 +902,16 @@
         <v>1.15</v>
       </c>
       <c r="G11" s="5" t="n">
+        <v>412226.78</v>
+      </c>
+      <c r="H11" s="5" t="n">
         <v>474060.8</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>412226.78</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>502916.67</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>578354.1800000001</v>
       </c>
     </row>
     <row r="12">
@@ -904,13 +940,16 @@
         <v>0.98</v>
       </c>
       <c r="G12" s="5" t="n">
+        <v>219603.83</v>
+      </c>
+      <c r="H12" s="5" t="n">
         <v>215211.75</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>219603.83</v>
       </c>
       <c r="I12" s="5" t="n">
         <v>267916.67</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>262558.34</v>
       </c>
     </row>
     <row r="13">
@@ -939,13 +978,16 @@
         <v>1.236</v>
       </c>
       <c r="G13" s="5" t="n">
+        <v>89125.67999999999</v>
+      </c>
+      <c r="H13" s="5" t="n">
         <v>110159.34</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>89125.67999999999</v>
       </c>
       <c r="I13" s="5" t="n">
         <v>108733.33</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>134394.39</v>
       </c>
     </row>
     <row r="14">
@@ -974,13 +1016,16 @@
         <v>1.472</v>
       </c>
       <c r="G14" s="5" t="n">
+        <v>89726.78</v>
+      </c>
+      <c r="H14" s="5" t="n">
         <v>132077.82</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>89726.78</v>
       </c>
       <c r="I14" s="5" t="n">
         <v>109466.67</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>161134.94</v>
       </c>
     </row>
     <row r="15">
@@ -1009,13 +1054,16 @@
         <v>2.869</v>
       </c>
       <c r="G15" s="5" t="n">
+        <v>98366.12</v>
+      </c>
+      <c r="H15" s="5" t="n">
         <v>282212.4</v>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v>98366.12</v>
       </c>
       <c r="I15" s="5" t="n">
         <v>120006.67</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>344299.13</v>
       </c>
     </row>
     <row r="16">
@@ -1044,13 +1092,16 @@
         <v>4.168</v>
       </c>
       <c r="G16" s="5" t="n">
+        <v>98366.12</v>
+      </c>
+      <c r="H16" s="5" t="n">
         <v>409989.99</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>98366.12</v>
       </c>
       <c r="I16" s="5" t="n">
         <v>120006.67</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>500187.79</v>
       </c>
     </row>
     <row r="17">
@@ -1079,13 +1130,16 @@
         <v>4.996</v>
       </c>
       <c r="G17" s="5" t="n">
+        <v>98366.12</v>
+      </c>
+      <c r="H17" s="5" t="n">
         <v>491437.14</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>98366.12</v>
       </c>
       <c r="I17" s="5" t="n">
         <v>120006.67</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>599553.3100000001</v>
       </c>
     </row>
     <row r="18">
@@ -1114,14 +1168,17 @@
         <v>4.996</v>
       </c>
       <c r="G18" s="5" t="n">
+        <v>90928.96000000001</v>
+      </c>
+      <c r="H18" s="5" t="n">
         <v>454281.08</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>90928.96000000001</v>
       </c>
       <c r="I18" s="5" t="n">
         <v>110933.33</v>
       </c>
+      <c r="J18" s="5" t="n">
+        <v>554222.92</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -1133,7 +1190,16 @@
         <v>27.942</v>
       </c>
       <c r="G19" s="8" t="n">
+        <v>147451.92</v>
+      </c>
+      <c r="H19" s="8" t="n">
         <v>4120101.43</v>
+      </c>
+      <c r="I19" s="8" t="n">
+        <v>179891.34</v>
+      </c>
+      <c r="J19" s="8" t="n">
+        <v>5026523.74</v>
       </c>
     </row>
     <row r="20">
@@ -1142,7 +1208,7 @@
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="G20" s="8" t="n">
+      <c r="H20" s="8" t="n">
         <v>4120101.43</v>
       </c>
     </row>
@@ -1152,7 +1218,7 @@
           <t>НМЦК с НДС 22% (справочно):</t>
         </is>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="J21" s="8" t="n">
         <v>5026523.74</v>
       </c>
     </row>
